--- a/practice/answers/q021.xlsx
+++ b/practice/answers/q021.xlsx
@@ -12531,14 +12531,14 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>(b) The mean (61.2) sits just below the median (62.2) -- a slight left skew, but the two are close enough that the distribution is roughly symmetric.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="64" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>(d) Manitoba wheat's CV is about 0.20 against 0.39 for Saskatchewan 2023 canola: relative to its average, a wheat yield here wanders about half as much, so a grower could count on a result near the average far more often.</t>
